--- a/reports/raw-views/assets/tables/micro_multi_all_lemma.xlsx
+++ b/reports/raw-views/assets/tables/micro_multi_all_lemma.xlsx
@@ -436,32 +436,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Analistas e IA</t>
+          <t>Analysts and AI</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Analistas e Autores</t>
+          <t>Analysts and Authors</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Analistas e Pares</t>
+          <t>Analysts and Peers</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>IA e Autores</t>
+          <t>AI and Authors</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>IA e Pares</t>
+          <t>AI and Peers</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Autores e Pares</t>
+          <t>Authors and Peers</t>
         </is>
       </c>
     </row>
